--- a/mlef_pipeline/results/DCR/SQUAMOUS/RWD_PYRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/DCR/SQUAMOUS/RWD_PYRAD/rwd-only/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.59 ± 0.09</t>
+          <t>0.61 ± 0.09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.33 ± 0.06</t>
+          <t>0.34 ± 0.06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.38 ± 0.46</t>
+          <t>0.39 ± 0.45</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.63 ± 0.46</t>
+          <t>0.62 ± 0.45</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,17 +498,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.62 ± 0.20</t>
+          <t>0.64 ± 0.20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.17 ± 0.26</t>
+          <t>0.23 ± 0.31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="F4" t="n">
